--- a/stories/arbres/TREE-SAN-015.xlsx
+++ b/stories/arbres/TREE-SAN-015.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo est dans la chambre. Un petit écran brille. Maman s'assoit sur le lit. Papa passe la tête. L'adulte dit fini. Hugo va éteindre. Puis il prend un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo a regardé une recette à la cuisine, sur l'écran. Maman dit : fini. L'adulte dit fini. Hugo éteint. Il pose l'écran. Maman dit : un autre jeu. Hugo ouvre un tiroir.</t>
+          <t>Hugo a regardé une recette à la cuisine, sur l'écran. Fini. L'adulte dit fini. Hugo éteint. Il pose l'écran. Un autre jeu. Hugo ouvre un tiroir.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,15 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a regardé une recette à la cuisine, sur l'écran.
+maman|Fini. L'adulte dit fini.
+narrateur|Hugo éteint. Il pose l'écran.
+maman|Un autre jeu.
+narrateur|Hugo ouvre un tiroir.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1861,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman dit fini. Que fait Hugo ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2034,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a éteint. L'adulte a dit fini. Un autre jeu commence, loin de l'écran.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2181,6 +2227,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -2345,6 +2396,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo prend le ballon rouge. L'écran est éteint. L'adulte a dit fini. Un autre jeu. Il roule le ballon vers papa.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2589,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2758,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Tom attrape le ballon. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2925,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3092,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Léa tape doucement. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3259,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3426,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sami fait rebondir. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3593,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3760,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo sort le seau bleu. L'écran est éteint. L'adulte a dit fini. Un autre jeu : remplir le seau de cuillères.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3857,6 +3953,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4021,6 +4122,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Tom pose une cuillère. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4289,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4456,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Léa compte les cuillères. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4623,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4790,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sami porte le seau. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4957,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5124,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo prend le doudou. L'écran est éteint. L'adulte a dit fini. Un autre jeu : habiller le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,6 +5317,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5345,6 +5486,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Tom tient le chapeau. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5507,6 +5653,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5669,6 +5820,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Léa boutonne. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5831,6 +5987,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5993,6 +6154,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sami fait une voix douce. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6155,6 +6321,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6179,7 +6350,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Hugo avait l'écran sur le banc du jardin. Papa dit : fini. L'adulte dit fini. Hugo éteint. Il rentre. Papa dit : un autre jeu, maintenant.</t>
+          <t>Hugo avait l'écran sur le banc du jardin. Fini. L'adulte dit fini. Hugo éteint. Il rentre. Un autre jeu, maintenant.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6317,6 +6488,14 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo avait l'écran sur le banc du jardin.
+papa|Fini. L'adulte dit fini.
+narrateur|Hugo éteint. Il rentre.
+papa|Un autre jeu, maintenant.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6493,6 +6672,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Papa dit fini. Que fait Hugo ?</t>
         </is>
       </c>
     </row>
@@ -6661,6 +6845,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a éteint dehors. L'adulte a dit fini. Un autre jeu l'attend.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6849,6 +7038,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -7013,6 +7207,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo lance le ballon rouge dans l'herbe. L'écran est éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7201,6 +7400,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7365,6 +7569,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Tom court après le ballon. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7527,6 +7736,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7689,6 +7903,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Léa arrête le ballon. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7851,6 +8070,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8013,6 +8237,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sami le relance. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8175,6 +8404,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8337,6 +8571,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo remplit le seau bleu de feuilles. L'écran est éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8525,6 +8764,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8689,6 +8933,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Tom ajoute une feuille. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8851,6 +9100,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9013,6 +9267,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Léa secoue le seau. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9175,6 +9434,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9337,6 +9601,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sami porte le seau. Hugo a éteint. L'adulte a dit fini. Un autre jeu. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9499,6 +9768,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9661,6 +9935,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo assied le doudou sur le banc. L'écran est éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9849,6 +10128,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10013,6 +10297,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Tom parle au doudou. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10175,6 +10464,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10337,6 +10631,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Léa lui met une feuille-chapeau. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10499,6 +10798,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10661,6 +10965,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sami chante. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10823,6 +11132,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10847,7 +11161,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Hugo est dans la chambre. Le dessin tourne. Maman dit : fini. L'adulte dit fini. Hugo éteint. L'écran devient noir. Maman dit : un autre jeu. Hugo cherche sous le lit.</t>
+          <t>Hugo est dans la chambre. Le dessin tourne. Fini. L'adulte dit fini. Hugo éteint. L'écran devient noir. Un autre jeu. Hugo cherche sous le lit.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10985,6 +11299,15 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo est dans la chambre. Le dessin tourne.
+maman|Fini. L'adulte dit fini.
+narrateur|Hugo éteint. L'écran devient noir.
+maman|Un autre jeu.
+narrateur|Hugo cherche sous le lit.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11165,6 +11488,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|L'adulte dit fini. Que fait Hugo ?</t>
         </is>
       </c>
     </row>
@@ -11333,6 +11661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a éteint dans la chambre. L'adulte a dit fini. Un autre jeu, sur le tapis.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11521,6 +11854,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -11685,6 +12023,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo fait rouler le ballon rouge sous la table. L'écran est éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11873,6 +12216,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12037,6 +12385,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'assoit en face. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12199,6 +12552,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12361,6 +12719,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Léa arrête le ballon avec le pied. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12523,6 +12886,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12685,6 +13053,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rit. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12847,6 +13220,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13009,6 +13387,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo range des cubes dans le seau bleu. L'écran est éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13197,6 +13580,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13361,6 +13749,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Tom pose un cube. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13523,6 +13916,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13685,6 +14083,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Léa trie les couleurs. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13847,6 +14250,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14009,6 +14417,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sami ferme le seau. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14171,6 +14584,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14333,6 +14751,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo câline le doudou. L'écran est éteint. L'adulte a dit fini. Un autre jeu : une histoire parlée.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14521,6 +14944,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14685,6 +15113,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Tom écoute. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14847,6 +15280,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15009,6 +15447,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Léa invente une voix. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15171,6 +15614,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15333,6 +15781,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sami tapote le doudou. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15495,6 +15948,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15513,7 +15971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15607,6 +16065,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-015.xlsx
+++ b/stories/arbres/TREE-SAN-015.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Hugo est dans la chambre. Un petit écran brille. Maman s'assoit sur le lit. Papa passe la tête. L'adulte dit fini. Hugo va éteindre. Puis il prend un autre jeu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
 narrateur|Hugo ouvre un tiroir.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1868,6 +1876,7 @@
           <t>narrateur|Maman dit fini. Que fait Hugo ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2039,6 +2048,7 @@
           <t>narrateur|Hugo a éteint. L'adulte a dit fini. Un autre jeu commence, loin de l'écran.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2234,6 +2244,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2401,6 +2412,7 @@
           <t>narrateur|Hugo prend le ballon rouge. L'écran est éteint. L'adulte a dit fini. Un autre jeu. Il roule le ballon vers papa.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2596,6 +2608,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2763,6 +2776,7 @@
           <t>narrateur|Tom attrape le ballon. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2930,6 +2944,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3097,6 +3112,7 @@
           <t>narrateur|Léa tape doucement. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3264,6 +3280,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3431,6 +3448,7 @@
           <t>narrateur|Sami fait rebondir. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3598,6 +3616,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3765,6 +3784,7 @@
           <t>narrateur|Hugo sort le seau bleu. L'écran est éteint. L'adulte a dit fini. Un autre jeu : remplir le seau de cuillères.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3960,6 +3980,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4127,6 +4148,7 @@
           <t>narrateur|Tom pose une cuillère. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4294,6 +4316,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4461,6 +4484,7 @@
           <t>narrateur|Léa compte les cuillères. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4628,6 +4652,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4795,6 +4820,7 @@
           <t>narrateur|Sami porte le seau. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4962,6 +4988,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5129,6 +5156,7 @@
           <t>narrateur|Hugo prend le doudou. L'écran est éteint. L'adulte a dit fini. Un autre jeu : habiller le doudou.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5324,6 +5352,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5491,6 +5520,7 @@
           <t>narrateur|Tom tient le chapeau. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5658,6 +5688,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5825,6 +5856,7 @@
           <t>narrateur|Léa boutonne. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5992,6 +6024,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6159,6 +6192,7 @@
           <t>narrateur|Sami fait une voix douce. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6326,6 +6360,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6496,6 +6531,7 @@
 papa|Un autre jeu, maintenant.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6679,6 +6715,7 @@
           <t>narrateur|Papa dit fini. Que fait Hugo ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6850,6 +6887,7 @@
           <t>narrateur|Hugo a éteint dehors. L'adulte a dit fini. Un autre jeu l'attend.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7045,6 +7083,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7212,6 +7251,7 @@
           <t>narrateur|Hugo lance le ballon rouge dans l'herbe. L'écran est éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7407,6 +7447,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7574,6 +7615,7 @@
           <t>narrateur|Tom court après le ballon. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7741,6 +7783,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7908,6 +7951,7 @@
           <t>narrateur|Léa arrête le ballon. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8075,6 +8119,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8242,6 +8287,7 @@
           <t>narrateur|Sami le relance. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8409,6 +8455,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8576,6 +8623,7 @@
           <t>narrateur|Hugo remplit le seau bleu de feuilles. L'écran est éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8771,6 +8819,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8938,6 +8987,7 @@
           <t>narrateur|Tom ajoute une feuille. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9105,6 +9155,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9272,6 +9323,7 @@
           <t>narrateur|Léa secoue le seau. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9439,6 +9491,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9606,6 +9659,7 @@
           <t>narrateur|Sami porte le seau. Hugo a éteint. L'adulte a dit fini. Un autre jeu. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9773,6 +9827,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9940,6 +9995,7 @@
           <t>narrateur|Hugo assied le doudou sur le banc. L'écran est éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10135,6 +10191,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10302,6 +10359,7 @@
           <t>narrateur|Tom parle au doudou. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10469,6 +10527,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10636,6 +10695,7 @@
           <t>narrateur|Léa lui met une feuille-chapeau. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10803,6 +10863,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10970,6 +11031,7 @@
           <t>narrateur|Sami chante. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11137,6 +11199,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11308,6 +11371,7 @@
 narrateur|Hugo cherche sous le lit.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11495,6 +11559,7 @@
           <t>narrateur|L'adulte dit fini. Que fait Hugo ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11666,6 +11731,7 @@
           <t>narrateur|Hugo a éteint dans la chambre. L'adulte a dit fini. Un autre jeu, sur le tapis.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11861,6 +11927,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12028,6 +12095,7 @@
           <t>narrateur|Hugo fait rouler le ballon rouge sous la table. L'écran est éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12223,6 +12291,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12390,6 +12459,7 @@
           <t>narrateur|Tom s'assoit en face. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12557,6 +12627,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12724,6 +12795,7 @@
           <t>narrateur|Léa arrête le ballon avec le pied. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12891,6 +12963,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13058,6 +13131,7 @@
           <t>narrateur|Sami rit. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13225,6 +13299,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13392,6 +13467,7 @@
           <t>narrateur|Hugo range des cubes dans le seau bleu. L'écran est éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13587,6 +13663,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13754,6 +13831,7 @@
           <t>narrateur|Tom pose un cube. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13921,6 +13999,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14088,6 +14167,7 @@
           <t>narrateur|Léa trie les couleurs. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14255,6 +14335,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14422,6 +14503,7 @@
           <t>narrateur|Sami ferme le seau. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14589,6 +14671,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14756,6 +14839,7 @@
           <t>narrateur|Hugo câline le doudou. L'écran est éteint. L'adulte a dit fini. Un autre jeu : une histoire parlée.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14951,6 +15035,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15118,6 +15203,7 @@
           <t>narrateur|Tom écoute. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15285,6 +15371,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15452,6 +15539,7 @@
           <t>narrateur|Léa invente une voix. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15619,6 +15707,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15786,6 +15875,7 @@
           <t>narrateur|Sami tapote le doudou. Hugo a éteint. L'adulte a dit fini. Un autre jeu.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15953,6 +16043,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15971,7 +16062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16072,6 +16163,20 @@
       <c r="A14" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16086,7 +16191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16273,6 +16378,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
